--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -16605,6 +16605,408 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16638,7 +17040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -16721,7 +17123,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -16731,7 +17133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -16751,7 +17153,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1058,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1212,9 +1206,6 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1464,7 +1455,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1866,7 +1857,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2268,7 +2259,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2670,7 +2661,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2965,9 +2956,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3368,7 +3356,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -3515,9 +3503,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3918,7 +3903,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4320,7 +4305,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4722,7 +4707,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5017,9 +5002,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5420,7 +5402,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5567,9 +5549,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5970,7 +5949,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6372,7 +6351,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6774,7 +6753,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7176,7 +7155,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -7323,9 +7302,6 @@
       <c r="O37" t="n">
         <v>3</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.001404739905698827</v>
       </c>
@@ -7471,9 +7447,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7619,9 +7592,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -8022,7 +7992,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8424,7 +8394,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8826,7 +8796,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9228,7 +9198,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9375,9 +9345,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9523,9 +9490,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9926,7 +9890,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10328,7 +10292,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10730,7 +10694,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11132,7 +11096,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11534,7 +11498,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11681,9 +11645,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12077,9 +12038,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -12225,9 +12183,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12376,9 +12331,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12628,7 +12580,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -12778,9 +12730,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13030,7 +12979,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13180,9 +13129,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13432,7 +13378,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13582,9 +13528,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13834,7 +13777,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13981,9 +13924,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14377,9 +14317,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14528,9 +14465,6 @@
       <c r="P75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14780,7 +14714,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14930,9 +14864,6 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -15182,7 +15113,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -15332,9 +15263,6 @@
       <c r="P79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15584,7 +15512,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -15734,9 +15662,6 @@
       <c r="P81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15986,7 +15911,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -16133,9 +16058,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16529,9 +16451,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16680,9 +16599,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16932,7 +16848,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -16923,6 +16923,405 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16956,7 +17355,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -17039,7 +17438,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -17049,7 +17448,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -17069,7 +17468,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -17322,6 +17322,405 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17355,7 +17754,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17837,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -17448,7 +17847,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -17468,7 +17867,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -14273,12 +14273,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14351,42 +14351,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14418,12 +14418,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -14462,9 +14462,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14473,82 +14470,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14558,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14627,98 +14610,23 @@
       <c r="P76" t="n">
         <v>0</v>
       </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -14812,7 +14720,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14847,7 +14755,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -14864,23 +14772,98 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -14974,7 +14957,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15026,98 +15009,23 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN78" t="b">
-        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -15211,7 +15119,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15246,7 +15154,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -15263,23 +15171,98 @@
       <c r="P79" t="n">
         <v>0</v>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -15373,7 +15356,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15425,98 +15408,23 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -15610,7 +15518,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15645,7 +15553,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -15662,23 +15570,98 @@
       <c r="P81" t="n">
         <v>0</v>
       </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -15772,7 +15755,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15824,98 +15807,23 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN82" t="b">
-        <v>1</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -16009,17 +15917,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -16044,12 +15952,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -16058,23 +15966,101 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P83" t="n">
+        <v>0</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -16093,7 +16079,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -16106,42 +16092,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16154,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16217,98 +16203,23 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN84" t="b">
-        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -16402,17 +16313,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -16451,76 +16362,165 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -16596,9 +16596,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16607,82 +16604,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16692,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16761,98 +16744,23 @@
       <c r="P87" t="n">
         <v>0</v>
       </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -16946,7 +16854,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16981,7 +16889,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -16998,23 +16906,98 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -17108,7 +17091,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17160,98 +17143,23 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN89" t="b">
-        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -17345,7 +17253,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17380,7 +17288,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -17397,23 +17305,98 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -17507,7 +17490,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17559,98 +17542,23 @@
       <c r="P91" t="n">
         <v>0</v>
       </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN91" t="b">
-        <v>1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -17716,6 +17624,243 @@
         </is>
       </c>
       <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -17837,7 +17982,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -17847,7 +17992,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -11994,12 +11994,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12038,12 +12038,9 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -12072,42 +12069,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12139,12 +12136,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12183,12 +12180,9 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -12217,42 +12211,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12284,12 +12278,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12314,7 +12308,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -12328,93 +12322,73 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12441,17 +12415,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -12476,7 +12450,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -12490,168 +12464,73 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP65" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV65" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12683,12 +12562,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -12713,7 +12592,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -12727,93 +12606,73 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12840,17 +12699,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -12875,7 +12734,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -12889,168 +12748,73 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV67" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13082,12 +12846,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13112,7 +12876,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -13126,93 +12890,73 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13239,17 +12983,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -13274,7 +13018,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -13288,168 +13032,73 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP69" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV69" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13481,12 +13130,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13511,7 +13160,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -13525,9 +13174,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13536,82 +13182,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13638,17 +13270,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -13673,7 +13305,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -13687,168 +13319,76 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN71" t="b">
-        <v>1</v>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13880,12 +13420,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -13910,12 +13450,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -13924,6 +13464,9 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13934,12 +13477,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -13959,7 +13502,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
@@ -13972,42 +13515,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14039,12 +13582,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14069,12 +13612,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14083,24 +13626,27 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Rubella congenital</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -14115,7 +13661,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -14125,7 +13671,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -14165,7 +13711,7 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -14193,7 +13739,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -14206,42 +13752,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14273,12 +13819,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14303,12 +13849,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -14317,6 +13863,9 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14325,68 +13874,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14413,17 +13976,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14448,12 +14011,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -14462,76 +14025,168 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14593,12 +14248,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -14755,12 +14410,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -14992,12 +14647,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -15154,12 +14809,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -15361,12 +15016,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15391,7 +15046,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -15405,9 +15060,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15418,12 +15070,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -15443,7 +15095,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -15456,42 +15108,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15523,12 +15175,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -15553,7 +15205,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -15567,27 +15219,24 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Congenital rubella syndrome</t>
+          <t>Rubella congenital</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -15602,7 +15251,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -15612,7 +15261,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -15652,7 +15301,7 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
+          <t>Australia NINDSS congenital rubella notifications.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -15680,7 +15329,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -15693,42 +15342,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15760,12 +15409,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15790,7 +15439,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -15804,93 +15453,73 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15917,17 +15546,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -15952,7 +15581,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -15966,168 +15595,73 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP83" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV83" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16159,12 +15693,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -16189,12 +15723,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -16203,50 +15737,33 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -16256,12 +15773,12 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -16276,12 +15793,12 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
@@ -16313,17 +15830,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -16348,12 +15865,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -16362,160 +15879,68 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP85" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="AT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV85" t="inlineStr">
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
@@ -16552,12 +15977,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -16582,12 +16007,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -16596,12 +16021,9 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -16630,42 +16052,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16697,12 +16119,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -16727,12 +16149,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -16741,93 +16163,73 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16854,17 +16256,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16889,12 +16291,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -16903,168 +16305,73 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP88" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV88" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17096,12 +16403,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -17126,12 +16433,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -17140,93 +16447,73 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17253,17 +16540,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -17288,12 +16575,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -17302,168 +16589,76 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17495,12 +16690,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17525,12 +16720,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -17539,9 +16734,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17550,82 +16742,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17652,7 +16830,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17687,12 +16865,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -17704,98 +16882,23 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN92" t="b">
-        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -17863,6 +16966,5248 @@
       <c r="BC92" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17899,7 +22244,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -17982,7 +22327,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -17992,7 +22337,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -18012,7 +22357,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
